--- a/public/data/contract_termination.xlsx
+++ b/public/data/contract_termination.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,13 +424,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>4284f0f9-e06b-4423-b1f2-55c6b671808a</v>
+        <v>6b7a880e-f770-407e-b49b-392f06ad1e52</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D2" t="str">
         <v>CTR-001-001</v>
@@ -447,13 +447,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>7ec99110-a34d-47f1-9fb4-8a8c3d747a90</v>
+        <v>36aed8c8-a3bc-4c5c-bcc2-f26627f9bf3b</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D3" t="str">
         <v>CTR-001-001</v>
@@ -470,177 +470,177 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>1133f891-e5b9-4739-9864-bd96c3b7784e</v>
+        <v>cd59bf2e-1e80-44a3-bf59-14fdd9b3a1da</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D4" t="str">
-        <v>CTR-002-001</v>
+        <v>CTR-001-002</v>
       </c>
       <c r="E4" t="str">
         <v>Notice period</v>
       </c>
       <c r="F4" t="str">
-        <v>90 days</v>
+        <v>180 days</v>
       </c>
       <c r="G4" t="str">
-        <v>Written notice</v>
+        <v>Charter longer notice</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>212afcc3-2e87-45c8-ada1-33aabfafd859</v>
+        <v>e3c0586a-b4d9-448b-9a24-214555b661ff</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D5" t="str">
-        <v>CTR-003-001</v>
+        <v>CTR-002-001</v>
       </c>
       <c r="E5" t="str">
         <v>Notice period</v>
       </c>
       <c r="F5" t="str">
-        <v>180 days</v>
+        <v>90 days</v>
       </c>
       <c r="G5" t="str">
-        <v>Charter requires longer notice</v>
+        <v>Written notice</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3422aad7-6dfb-4b0f-a455-445b80dcfb5a</v>
+        <v>7993c0ce-48dd-4e6a-a571-584c4b242e7e</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D6" t="str">
-        <v>CTR-005-001</v>
+        <v>CTR-003-001</v>
       </c>
       <c r="E6" t="str">
         <v>Notice period</v>
       </c>
       <c r="F6" t="str">
-        <v>90 days</v>
+        <v>180 days</v>
       </c>
       <c r="G6" t="str">
-        <v>Standard Marriott terms</v>
+        <v>Charter requires longer notice</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>04007d1f-ff1d-45d3-bce8-1afd954c122b</v>
+        <v>a22b6164-4da8-4354-9c05-5761e092c477</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D7" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-001</v>
       </c>
       <c r="E7" t="str">
-        <v>Notice period</v>
+        <v>Early termination fee</v>
       </c>
       <c r="F7" t="str">
-        <v>90 days</v>
+        <v>6 months charter fees</v>
       </c>
       <c r="G7" t="str">
-        <v>Written notice to both parties</v>
+        <v>Due to dedicated asset</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>39d09df9-b87e-489b-9eae-538eddceaf0b</v>
+        <v>6d0a3447-553a-4a02-8405-39de6a3d798f</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D8" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-002</v>
       </c>
       <c r="E8" t="str">
-        <v>Early termination fee</v>
+        <v>Notice period</v>
       </c>
       <c r="F8" t="str">
-        <v>3 months revenue</v>
+        <v>90 days</v>
       </c>
       <c r="G8" t="str">
-        <v>Trailing 3-month average</v>
+        <v>Transfer standard notice</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>85e94f93-de52-4bd1-a841-a6fb97b5a4a4</v>
+        <v>2ad6cfd2-822a-4cb8-a8a2-da5ca4a5834c</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D9" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-003</v>
       </c>
       <c r="E9" t="str">
-        <v>Force majeure</v>
+        <v>Notice period</v>
       </c>
       <c r="F9" t="str">
-        <v>No penalty</v>
+        <v>180 days</v>
       </c>
       <c r="G9" t="str">
-        <v>Natural disaster, pandemic, govt order</v>
+        <v>Signed charter notice</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>43059a8a-5d6d-4c2c-98d6-761874884ccb</v>
+        <v>8a37c4c6-79ee-4496-957d-d0b8ec7dc142</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D10" t="str">
-        <v>CTR-007-001</v>
+        <v>CTR-005-001</v>
       </c>
       <c r="E10" t="str">
         <v>Notice period</v>
       </c>
       <c r="F10" t="str">
-        <v>60 days</v>
+        <v>90 days</v>
       </c>
       <c r="G10" t="str">
-        <v>Speedboat shorter notice</v>
+        <v>Standard Marriott terms</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>6346fb8c-e1e5-400e-b804-f94c101d752e</v>
+        <v>09f30c7a-9941-44bc-96d2-321c56dc5b5b</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D11" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-005-002</v>
       </c>
       <c r="E11" t="str">
         <v>Notice period</v>
@@ -649,81 +649,334 @@
         <v>180 days</v>
       </c>
       <c r="G11" t="str">
-        <v>Charter termination notice</v>
+        <v>Charter notice</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2a352284-6a4d-4d1e-b758-62247dfb08d5</v>
+        <v>9a1e7c8d-14c9-4ae7-ab4c-22fba3d953ff</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D12" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-006-001</v>
       </c>
       <c r="E12" t="str">
-        <v>Early termination fee</v>
+        <v>Notice period</v>
       </c>
       <c r="F12" t="str">
-        <v>6 months charter fees</v>
+        <v>90 days</v>
       </c>
       <c r="G12" t="str">
-        <v>Due to dedicated asset</v>
+        <v>Written notice to both parties</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>64cdfe79-f2d6-4559-b141-795f0cf48236</v>
+        <v>cfef5b68-f170-4ed2-abbb-6f68bdf45b76</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D13" t="str">
-        <v>CTR-009-001</v>
+        <v>CTR-006-001</v>
       </c>
       <c r="E13" t="str">
-        <v>Notice period</v>
+        <v>Early termination fee</v>
       </c>
       <c r="F13" t="str">
-        <v>60 days</v>
+        <v>3 months revenue</v>
       </c>
       <c r="G13" t="str">
-        <v>Speedboat notice period</v>
+        <v>Trailing 3-month average</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>9e26280a-094b-40e2-89e8-e036e67d7062</v>
+        <v>1263b9ab-a0c1-469a-b1c0-80232b3060f8</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D14" t="str">
+        <v>CTR-006-001</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Force majeure</v>
+      </c>
+      <c r="F14" t="str">
+        <v>No penalty</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Natural disaster, pandemic, govt order</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>0347ab65-186c-486e-83ba-f3467222667f</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D15" t="str">
+        <v>CTR-006-002</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Notice period</v>
+      </c>
+      <c r="F15" t="str">
+        <v>180 days</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Charter notice</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5213000b-804c-4b87-b0e4-239258d18aca</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D16" t="str">
+        <v>CTR-006-003</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Notice period</v>
+      </c>
+      <c r="F16" t="str">
+        <v>180 days</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Signed charter notice</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>74b7e947-feb7-4943-8d59-71f354a44916</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D17" t="str">
+        <v>CTR-006-003</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Early termination fee</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Full remaining contract value</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Signed charter penalty</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>ae1774fb-62fa-4b0b-9992-fc6ac2d183bd</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D18" t="str">
+        <v>CTR-007-001</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Notice period</v>
+      </c>
+      <c r="F18" t="str">
+        <v>60 days</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Speedboat shorter notice</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>ed5a7ddc-6abf-40f8-9954-2db5a873e430</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D19" t="str">
+        <v>CTR-007-002</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Notice period</v>
+      </c>
+      <c r="F19" t="str">
+        <v>90 days</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Seaplane standard</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>e8ea776f-ea84-48e4-a084-9062ea14317c</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D20" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Notice period</v>
+      </c>
+      <c r="F20" t="str">
+        <v>180 days</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Charter termination notice</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>d9861bc5-83b9-403d-8979-e6dd95d687ef</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D21" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Early termination fee</v>
+      </c>
+      <c r="F21" t="str">
+        <v>6 months charter fees</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Due to dedicated asset</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>7e33d2f6-33a8-4f79-b9e3-5dabc79ab17e</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D22" t="str">
+        <v>CTR-008-002</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Notice period</v>
+      </c>
+      <c r="F22" t="str">
+        <v>90 days</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Transfer notice</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>cba6f2f2-1fd4-4a42-b40d-39b71eed0352</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D23" t="str">
+        <v>CTR-009-001</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Notice period</v>
+      </c>
+      <c r="F23" t="str">
+        <v>60 days</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Speedboat notice period</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>e070cecd-13b3-4c2b-9cf3-2d1399222447</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C24" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D24" t="str">
         <v>CTR-010-001</v>
       </c>
-      <c r="E14" t="str">
-        <v>Notice period</v>
-      </c>
-      <c r="F14" t="str">
+      <c r="E24" t="str">
+        <v>Notice period</v>
+      </c>
+      <c r="F24" t="str">
         <v>180 days</v>
       </c>
-      <c r="G14" t="str">
+      <c r="G24" t="str">
         <v>Charter notice</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>599a0965-f065-4c49-8f38-0b1edff3761e</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C25" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D25" t="str">
+        <v>CTR-010-002</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Notice period</v>
+      </c>
+      <c r="F25" t="str">
+        <v>90 days</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Transfer notice</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G25"/>
   </ignoredErrors>
 </worksheet>
 </file>